--- a/data/trans_orig/IP36BS1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP36BS1-Estudios-trans_orig.xlsx
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>8958</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14634</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>68,6%</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6697</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>58,04%</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>605</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>579</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -2545,12 +2545,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>11296</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>59,79%</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4474,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>20514</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,97%</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4602,12 +4602,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4637,12 +4637,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>24451</t>
+          <t>24768</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,5%</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>505</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>709</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>51,1%</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>482</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15430</t>
+          <t>15087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18056</t>
+          <t>18848</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29906</t>
+          <t>30486</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,89%</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13821</t>
+          <t>14086</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11543</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>44,81%</t>
         </is>
       </c>
     </row>
@@ -8111,12 +8111,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -8224,12 +8224,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22110</t>
+          <t>22190</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22926</t>
+          <t>22917</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>27705</t>
+          <t>26925</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>41713</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -8377,7 +8377,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -8676,12 +8676,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8726,12 +8726,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>19848</t>
+          <t>21214</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -8789,12 +8789,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>11111</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>17686</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8874,12 +8874,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -8902,12 +8902,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>10082</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>16351</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -9476,12 +9476,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9491,12 +9491,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9511,12 +9511,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>570</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9526,12 +9526,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1776</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -10076,12 +10076,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10091,12 +10091,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10111,12 +10111,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,17%</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10169,12 +10169,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>59,24%</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10454,12 +10454,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -10497,12 +10497,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10512,12 +10512,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10532,12 +10532,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6860</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15142</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10567,12 +10567,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22508</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,16%</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -10949,12 +10949,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10999,12 +10999,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>16029</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11034,12 +11034,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11132,12 +11132,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>594</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -11175,12 +11175,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11210,12 +11210,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>14670</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11245,12 +11245,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>8512</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19165</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11260,12 +11260,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,58%</t>
         </is>
       </c>
     </row>
@@ -11445,7 +11445,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11588,12 +11588,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11603,12 +11603,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -12201,7 +12201,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12246,12 +12246,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12281,12 +12281,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -12539,12 +12539,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12554,12 +12554,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12574,12 +12574,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>20049</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12589,12 +12589,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12609,12 +12609,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>17385</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12624,12 +12624,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -12805,7 +12805,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13026,12 +13026,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13041,12 +13041,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -13104,12 +13104,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13119,12 +13119,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13139,12 +13139,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>11225</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13698</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -13217,12 +13217,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13232,12 +13232,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13252,12 +13252,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>23331</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13267,12 +13267,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>31113</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -13826,12 +13826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>382</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13841,12 +13841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13861,12 +13861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13876,12 +13876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -13904,12 +13904,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13919,12 +13919,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13939,12 +13939,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13974,12 +13974,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14452</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13989,12 +13989,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -14248,7 +14248,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14283,7 +14283,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14313,12 +14313,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14328,12 +14328,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>473</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14371,12 +14371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14391,12 +14391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14406,12 +14406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14426,12 +14426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14441,12 +14441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>51,38%</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14489,7 +14489,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14539,12 +14539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6697</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14554,12 +14554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -14812,12 +14812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14827,12 +14827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14882,12 +14882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>9592</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14897,12 +14897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -14925,12 +14925,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14940,12 +14940,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14960,12 +14960,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14517</t>
+          <t>14865</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14975,12 +14975,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14995,12 +14995,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>23265</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15010,12 +15010,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15186,12 +15186,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>10016</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15201,12 +15201,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15221,12 +15221,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>12301</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15236,12 +15236,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -15264,12 +15264,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15279,12 +15279,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15299,12 +15299,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15314,12 +15314,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15334,12 +15334,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22712</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -15377,12 +15377,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15392,12 +15392,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15412,12 +15412,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15427,12 +15427,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15447,12 +15447,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14528</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15462,12 +15462,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -15490,12 +15490,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15505,12 +15505,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15525,12 +15525,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15540,12 +15540,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>12499</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15575,12 +15575,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>68,55%</t>
         </is>
       </c>
     </row>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16355,12 +16355,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>409</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16370,12 +16370,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16566,7 +16566,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16601,7 +16601,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>76,86%</t>
         </is>
       </c>
     </row>
@@ -16854,12 +16854,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16869,12 +16869,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16889,12 +16889,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>394</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16904,12 +16904,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16924,12 +16924,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12015</t>
+          <t>11199</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16939,12 +16939,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -16967,12 +16967,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>20750</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -16982,12 +16982,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17002,12 +17002,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17017,12 +17017,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17037,12 +17037,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>35003</t>
+          <t>35501</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17052,12 +17052,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -17198,7 +17198,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17213,7 +17213,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17228,12 +17228,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17243,12 +17243,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17263,12 +17263,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17278,12 +17278,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -17306,12 +17306,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17321,12 +17321,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17341,12 +17341,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16361</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17356,12 +17356,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17376,12 +17376,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>28637</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17391,12 +17391,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -17419,12 +17419,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17434,12 +17434,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17454,12 +17454,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17469,12 +17469,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17489,12 +17489,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>24265</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17504,12 +17504,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -17532,12 +17532,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>9883</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17567,12 +17567,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17582,12 +17582,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17602,12 +17602,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6737</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>18211</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17617,12 +17617,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
